--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.66500053641731</v>
+        <v>9.370562587167813</v>
       </c>
       <c r="D2" t="n">
-        <v>58.14495299803298</v>
+        <v>9.448554862180361</v>
       </c>
       <c r="E2" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F2" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.88839955719725</v>
+        <v>7.781864928044553</v>
       </c>
       <c r="D3" t="n">
-        <v>47.62563804965734</v>
+        <v>7.739166183069318</v>
       </c>
       <c r="E3" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F3" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>88.08100954393483</v>
+        <v>14.31316405088941</v>
       </c>
       <c r="D4" t="n">
-        <v>88.54576673553208</v>
+        <v>14.38868709452396</v>
       </c>
       <c r="E4" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F4" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.16007721271936</v>
+        <v>6.363512547066896</v>
       </c>
       <c r="D5" t="n">
-        <v>39.17603669863172</v>
+        <v>6.366105963527654</v>
       </c>
       <c r="E5" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F5" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.39443834466515</v>
+        <v>5.264096231008088</v>
       </c>
       <c r="D6" t="n">
-        <v>32.50671094028729</v>
+        <v>5.282340527796685</v>
       </c>
       <c r="E6" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F6" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.62281640121149</v>
+        <v>5.138707665196867</v>
       </c>
       <c r="D7" t="n">
-        <v>31.57514229421143</v>
+        <v>5.130960622809357</v>
       </c>
       <c r="E7" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F7" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.46132700734607</v>
+        <v>2.512465638693737</v>
       </c>
       <c r="D8" t="n">
-        <v>15.34583621555953</v>
+        <v>2.493698385028424</v>
       </c>
       <c r="E8" t="n">
-        <v>21.60735090555359</v>
+        <v>3.511194522152458</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79415587474791</v>
+        <v>3.541550329646537</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
